--- a/data/IKPA_JULI_2025.xlsx
+++ b/data/IKPA_JULI_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,17 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Uraian Satker Final</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Satker</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -626,7 +636,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (401944)</t>
+          <t>PA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PA MARTAPURA (401944)</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -711,7 +731,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
+          <t>PA MUARADUA</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>PA MUARADUA (401945)</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -796,7 +826,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440507)</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -881,7 +921,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>RUTAN BATURAJA</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>RUTAN BATURAJA (692339)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -966,7 +1016,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
+          <t>PA BATURAJA</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>PA BATURAJA (402267)</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1111,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
+          <t>PA BATURAJA</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>PA BATURAJA (402268)</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1206,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440505)</t>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440505)</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1301,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
+          <t>PA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>PA MARTAPURA (403409)</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1396,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
+          <t>KPPN BATURAJA</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA (527975)</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1491,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN (667215)</t>
+          <t>BPS OKUS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>BPS OKUS (667215)</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1586,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN (665307)</t>
+          <t>POLRES OKUS</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>POLRES OKUS (665307)</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1681,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
+          <t>KPP BATURAJA</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>KPP BATURAJA (410574)</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1776,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR (668529)</t>
+          <t>BPS OKUT</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>BPS OKUT (668529)</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1871,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU (641681)</t>
+          <t>POLRES OKU</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>POLRES OKU (641681)</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1966,17 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440504)</t>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440504)</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1901,7 +2061,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
+          <t>BPS OKU</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>BPS OKU (428258)</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2156,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418456)</t>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418456)</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2251,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (111071)</t>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (111071)</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2281,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>'007130</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2156,7 +2346,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
+          <t>KEJARI  OKU</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>KEJARI  OKU ('007130)</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2441,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (403410)</t>
+          <t>PA  MUARADUA</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>PA  MUARADUA (403410)</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2471,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2326,7 +2536,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
+          <t>KEJARI OKUT</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>KEJARI OKUT ('007190)</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2631,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN (670561)</t>
+          <t>BPN OKUS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>BPN OKUS (670561)</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2496,7 +2726,17 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (098963)</t>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>PN BATURAJA ('098963)</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2821,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR (656560)</t>
+          <t>KPU OKUT</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>KPU OKUT (656560)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2916,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK (692625)</t>
+          <t>BAPAS OKU INDUK</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>BAPAS OKU INDUK (692625)</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2751,7 +3011,17 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440506)</t>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440506)</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2836,7 +3106,17 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666505)</t>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666505)</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -2921,7 +3201,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR (418471)</t>
+          <t>MTSN 2 OKUT</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUT (418471)</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3296,17 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR (553099)</t>
+          <t>MTSN 3 OKUT</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT (553099)</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3391,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD (685001)</t>
+          <t>PUSLATPUR AD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>PUSLATPUR AD (685001)</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3486,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN (656574)</t>
+          <t>KPU OKUS</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>KPU OKUS (656574)</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3516,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3261,7 +3581,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KEJARI  OKUS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>KEJARI  OKUS ('007208)</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3676,17 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666501)</t>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666501)</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3771,17 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN (669055)</t>
+          <t>BPN OKUT</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>BPN OKUT (669055)</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3866,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA (692334)</t>
+          <t>LAPAS MUARA DUA</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>LAPAS MUARA DUA (692334)</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3961,17 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR (665292)</t>
+          <t>POLRES OKUT</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>POLRES OKUT (665292)</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3686,7 +4056,17 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440502)</t>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440502)</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3771,7 +4151,17 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418458)</t>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418458)</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3856,7 +4246,17 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666504)</t>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666504)</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -3941,7 +4341,17 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA (692340)</t>
+          <t>LAPAS MARTAPURA</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>LAPAS MARTAPURA (692340)</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4436,17 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (662127)</t>
+          <t>MAN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS (662127)</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4531,17 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU (424245)</t>
+          <t>MAN 1 OKU</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU (424245)</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4626,17 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ (344894)</t>
+          <t>RUMKIT NOESMIR</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>RUMKIT NOESMIR (344894)</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4721,17 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN (661192)</t>
+          <t>MTSN 4 OKUS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUS (661192)</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4816,17 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU (431142)</t>
+          <t>BPN OKU</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>BPN OKU (431142)</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4911,17 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (418462)</t>
+          <t>MTSN 2 OKUS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUS (418462)</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4536,7 +5006,17 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666503)</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4621,7 +5101,17 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN (686503)</t>
+          <t>BAWASLU OKUS</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>BAWASLU OKUS (686503)</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4706,7 +5196,17 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU (656553)</t>
+          <t>KPU OKU</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>KPU OKU (656553)</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4791,7 +5291,17 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (424967)</t>
+          <t>MTSN 1 OKUT</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUT (424967)</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4876,7 +5386,17 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418459)</t>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418459)</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -4961,7 +5481,17 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU (426050)</t>
+          <t>MTSN 1 OKU</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKU (426050)</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5576,17 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (426066)</t>
+          <t>MAN 1 OKUT</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUT (426066)</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5671,17 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA (692725)</t>
+          <t>RUPBASAN BATURAJA</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>RUPBASAN BATURAJA (692725)</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5766,17 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440503)</t>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440503)</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5861,17 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (597558)</t>
+          <t>MAN 2 OKUS</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>MAN 2 OKUS (597558)</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5956,17 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (553792)</t>
+          <t>MTSN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUS (553792)</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5471,7 +6051,17 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA (690801)</t>
+          <t>LOKA LABKESMAS</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>LOKA LABKESMAS (690801)</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5556,7 +6146,17 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR (111079)</t>
+          <t>BNN OKUT</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>BNN OKUT (111079)</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5576,7 +6176,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5641,7 +6241,17 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (099228)</t>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>PN BATURAJA ('099228)</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5726,7 +6336,17 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666502)</t>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666502)</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5811,7 +6431,17 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418457)</t>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418457)</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5896,7 +6526,17 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU (419006)</t>
+          <t>BAWASLU OKU</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>BAWASLU OKU (419006)</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -5981,7 +6621,17 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR (597480)</t>
+          <t>MTSN 4 OKUT</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUT (597480)</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6716,17 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418461)</t>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418461)</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6811,17 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666507)</t>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666507)</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6906,17 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN (574370)</t>
+          <t>MTSN 3 OKUS</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUS (574370)</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
@@ -6321,7 +7001,17 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR (691653)</t>
+          <t>DISNAKERTRANS OKUT</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>DISNAKERTRANS OKUT (691653)</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>
